--- a/survey_templates/043_humble_hungry_smart_survey--survey_templates.xlsx
+++ b/survey_templates/043_humble_hungry_smart_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>team_member_position</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,24 +538,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team Member Name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Please enter team member name</t>
-        </is>
-      </c>
+          <t>How would you describe this team member</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -570,19 +566,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>rate1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team Member Position</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Select one of the options</t>
-        </is>
-      </c>
+          <t>Rate this team member</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -592,101 +584,89 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>rate2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What does this team member do</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Please enter short description of the team member role</t>
-        </is>
-      </c>
+          <t>Rate2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>rate3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rate this team member</t>
+          <t>Rate3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_role</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How would you describe this team member</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>What does this team member do</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rate this team member</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Select one of the options</t>
-        </is>
-      </c>
+          <t>Enter a valid date</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -696,24 +676,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rate this team member</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Select one of the options</t>
-        </is>
-      </c>
+          <t>Enter a valid time</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -723,24 +699,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rate this team member</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Select one of the options</t>
-        </is>
-      </c>
+          <t>Enter a valid email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -755,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_rating</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rate this team member</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Enter value with up to 2 decimal places</t>
-        </is>
-      </c>
+          <t>Enter a numerical value</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -777,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_option</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rate this team member</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Please enter valid date</t>
-        </is>
-      </c>
+          <t>Select a suitable option</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -804,52 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>team_member_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rate this team member</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Please enter valid time</t>
-        </is>
-      </c>
+          <t>Team Member Name</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rate this team member</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Please enter valid email</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -866,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -894,357 +827,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>team_member_description_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>humble</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Humble</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>team_member_description_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>member</t>
+          <t>hungry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Hungry</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>team_member_description_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>smart</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Smart</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>humble</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Humble</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hungry</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hungry</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>smart</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Smart</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>rate3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>team_member_option_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>team_member_option_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>name_choices</t>
+          <t>team_member_option_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
